--- a/data/test.xlsx
+++ b/data/test.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>人力资源管理数据驾驶舱（测试）</t>
+          <t>人力资源管理数据驾驶舱</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#1E5BAA</t>
+          <t>#1e5baa</t>
         </is>
       </c>
     </row>
@@ -493,46 +493,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>区域</t>
+          <t>section</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>region</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>状态</t>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>region_tree</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>广州分行</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>37</v>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>总行本部</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>一级部门</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>营业</t>
         </is>
@@ -541,18 +551,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>region_tree</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>海珠支行</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>22</v>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>总行本部</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>二级部门</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>营业</t>
         </is>
@@ -561,18 +576,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>region_tree</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>天河支行</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>总行直属</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>一级部门</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>营业</t>
         </is>
@@ -581,18 +601,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>异地</t>
+          <t>region_tree</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>深圳分行</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>广州地区</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>广州分行</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>37</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>营业</t>
         </is>
@@ -601,18 +626,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>异地</t>
+          <t>region_tree</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>佛山分行</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>12</v>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>广州地区</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>海珠中心支行</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>营业</t>
         </is>
@@ -621,18 +651,423 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>异地</t>
+          <t>region_tree</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>广州地区</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>天河中心支行</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>广州地区</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>白云中心支行</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>广州地区</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>开发区中心支行</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>广州地区</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>增城中心支行</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>广州地区</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>南沙分行</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>广州地区</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>科技支行</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>广州地区</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>行总营业部</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>异地地区</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>深圳分行</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>异地地区</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>佛山分行</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>异地地区</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>南京分行</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D16" t="n">
         <v>9</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>异地地区</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>惠州分行</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>异地地区</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>江门分行</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>异地地区</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>中山分行</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>异地地区</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>肇庆分行</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>异地地区</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>东莞分行</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>异地地区</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>横琴分行</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>region_tree</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>异地地区</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>清远分行</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>营业</t>
         </is>
@@ -649,282 +1084,316 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>维度</t>
+          <t>section</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>label</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>value</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>年龄</t>
+          <t>headcount_total</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30岁以下</t>
+          <t>正式员工</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1526</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.2586</v>
+        <v>5901</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>含劳务派遣 6589</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>年龄</t>
+          <t>headcount_operating</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31-40岁</t>
+          <t>经营机构</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2851</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.4831</v>
+        <v>4709</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>占 79.80%</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>年龄</t>
+          <t>headcount_ratio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>41-50岁</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1123</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1903</v>
+          <t>前中后台</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1:0.73</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>前 3254 : 中后台 2372</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>年龄</t>
+          <t>age_distribution</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>51岁以上</t>
+          <t>30岁以下</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>401</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.068</v>
-      </c>
+        <v>1526</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>学历</t>
+          <t>age_distribution</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>硕士及以上</t>
+          <t>31-40岁</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1031</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.1747</v>
-      </c>
+        <v>2851</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>学历</t>
+          <t>age_distribution</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>本科</t>
+          <t>41-50岁</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4514</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.765</v>
-      </c>
+        <v>1123</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>学历</t>
+          <t>age_distribution</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>专科</t>
+          <t>51岁以上</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>326</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.0552</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>学历</t>
+          <t>edu_distribution</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>专科以下</t>
+          <t>硕士及以上</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.0051</v>
-      </c>
+        <v>1031</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>性别</t>
+          <t>edu_distribution</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>本科</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2717</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.4604</v>
-      </c>
+        <v>4514</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>性别</t>
+          <t>edu_distribution</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>专科</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3184</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.5396</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>客户经理</t>
+          <t>edu_distribution</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>对公</t>
+          <t>专科以下</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>850</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.5024</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>客户经理</t>
+          <t>gender_distribution</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>个人</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>390</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.2305</v>
-      </c>
+        <v>2717</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>客户经理</t>
+          <t>gender_distribution</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>个贷</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>359</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.2122</v>
-      </c>
+        <v>3184</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>客户经理</t>
+          <t>customer_managers</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>微贷</t>
+          <t>对公客户经理</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>850</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>customer_managers</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>个人客户经理</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>390</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>customer_managers</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>个贷客户经理</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>359</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>customer_managers</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>微贷客户经理</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>93</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.055</v>
-      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -937,125 +1406,225 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>指标</t>
+          <t>section</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>计划</t>
+          <t>label</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>实际</t>
+          <t>value</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>完成率</t>
+          <t>sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>腾笼换鸟</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>410</v>
+          <t>social_hire_total</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>社招入职</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>201</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.5</v>
+        <v>34</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026 年以来</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>绩差退出</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>96</v>
+          <t>campus_hire_total</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>校招签约</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.46</v>
+        <v>721</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>已签约/签约中</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>社招入职</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
+          <t>exit_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>累计退出</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
+        <v>202</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1-5 月</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>校招签约</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+          <t>campus_funnel</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>全年目标</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>659</v>
       </c>
-      <c r="C5" t="n">
-        <v>721</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.09</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>总退出</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
+          <t>campus_funnel</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>已签约</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>202</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
+        <v>721</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>劳动仲裁</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
+          <t>campus_funnel</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>管培生</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>campus_funnel</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>金融科技岗</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>54</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>campus_funnel</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>分行管培生</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>112</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>campus_funnel</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>英才岗</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>469</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>teng_long_huan_yao</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>腾笼换鸟</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>201</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>全年任务 410</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>poor_perf_exit</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>绩差退出</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>目标 50%（96人）</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1069,141 +1638,296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>分类</t>
+          <t>section</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>总职数</t>
+          <t>label</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>已配</t>
+          <t>value</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>空缺</t>
+          <t>sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>中层正职</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>54</v>
+          <t>headcount_total</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>中层总职数</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>中层副职</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>157</v>
+          <t>headcount_filled</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>已配备</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>144</v>
-      </c>
-      <c r="D3" t="n">
-        <v>13</v>
+        <v>194</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>总行部门</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>100</v>
+          <t>headcount_vacancy</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>空缺</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>93</v>
-      </c>
-      <c r="D4" t="n">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>经营机构</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>111</v>
+          <t>config_table</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>市管领导干部</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>提拔</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>94</v>
+          <t>config_table</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>高管人员</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>降免</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
+          <t>config_table</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>派驻纪检监察组</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>config_table</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>中层正职</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>54</v>
+      </c>
+      <c r="D8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>config_table</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>中层副职</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>157</v>
+      </c>
+      <c r="D9" t="n">
+        <v>144</v>
+      </c>
+      <c r="E9" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>config_table</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>总行部门</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>93</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>config_table</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>经营机构</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>111</v>
+      </c>
+      <c r="D11" t="n">
+        <v>101</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adjustments</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>提拔</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>94</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>人次</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adjustments</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>降免职</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>14</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>人次</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adjustments</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>到龄转岗</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
+      <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>人次</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1217,128 +1941,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>指标</t>
+          <t>section</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>label</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>单位</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025年工资总额</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>15</v>
+          <t>salary_total</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025 年工资总额</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>亿元</t>
-        </is>
-      </c>
+          <t>15 亿元</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>salary_per_capita</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>人均薪酬</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>24.3</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>万元</t>
+          <t>24.3 万元</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>含预发 2026 开门红 0.3 亿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026年1-5月发放</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4.2</v>
+          <t>pension_balance</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>企业年金余额</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>17.44 亿元</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>企业年金余额</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>17.44</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>亿元</t>
+          <t>tou_lang_count</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>头狼评选</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>129</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026 Q1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>补充医疗节余</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>亿元</t>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>监测人数</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>95</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>班子成员</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>履职监测黑榜</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>15</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>人次</t>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>监测人次</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>113</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>业绩监测</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>头狼评选</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>129</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>人</t>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>黑榜人数</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>督导函</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>黑榜人次</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>首次触发</t>
         </is>
       </c>
     </row>
@@ -1353,174 +2139,278 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>部门/项目</t>
+          <t>section</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>计划</t>
+          <t>label</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>value</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>百分比</t>
+          <t>sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>能力大提升</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>983</v>
+          <t>training_total</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>能力大提升项目</t>
+        </is>
       </c>
       <c r="C2" t="n">
         <v>983</v>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>key_projects</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>重点培训项目</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>55</v>
       </c>
-      <c r="C3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.5806</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>董事会办公室</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
+          <t>exam_count</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>上岗资格人次</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
+        <v>1878</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>35 场次</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>私人银行部</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
+          <t>key_projects_pct</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>重点项目执行率</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>100</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
+        <v>0.5806</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>已完成 32/55</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>金融同业部</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
+          <t>dept_execution</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>董事会办公室</t>
+        </is>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>金融科技部</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+          <t>dept_execution</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>私人银行部</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>100</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>内控合规部</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+          <t>dept_execution</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>金融同业部</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>运营管理部</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+          <t>dept_execution</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>金融市场部</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>100</v>
       </c>
-      <c r="C9" t="n">
-        <v>14</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1429</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>上岗资格</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>35</v>
+          <t>dept_execution</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>战略客户部</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>1878</v>
-      </c>
-      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dept_execution</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>消保部</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dept_execution</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>机关纪委</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>dept_execution</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>安全保卫部</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dept_execution</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>金融科技部</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>0</v>
       </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dept_execution</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>内控合规部</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dept_execution</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>运营管理部</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/test.xlsx
+++ b/data/test.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,572 +504,617 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>label</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>branch</t>
+          <t>value</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
+          <t>sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>headquarters</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>总行本部</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>一级部门</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+          <t>总行本部一级部门</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>28</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>营业</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>个</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>headquarters</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>总行本部</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>二级部门</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>13</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>总行直属一级部门</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>个</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>headquarters</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>总行直属</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>一级部门</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>总行直属二级部门</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>个</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branches</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>广州地区</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>广州分行</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>37</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>分行级机构</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>家（含总行营业部、信用卡中心）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branches</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>广州地区</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>海珠中心支行</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>22</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>全行网点</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>183</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branches</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>广州地区</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>天河中心支行</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>14</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>正常营业</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>179</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branches</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>广州地区</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>白云中心支行</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>临时停业</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_guangzhou</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>广州地区</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>开发区中心支行</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>行总营业部</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_guangzhou</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>广州地区</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>增城中心支行</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>广州分行</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>37</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_guangzhou</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>广州地区</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>南沙分行</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>海珠中心支行</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_guangzhou</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>广州地区</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>科技支行</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>天河中心支行</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_guangzhou</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>广州地区</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>行总营业部</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>白云中心支行</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_guangzhou</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>异地地区</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>深圳分行</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>开发区中心支行</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_guangzhou</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>异地地区</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>佛山分行</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>增城中心支行</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_guangzhou</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>异地地区</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>南京分行</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>9</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>南沙分行</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_guangzhou</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>异地地区</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>惠州分行</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>科技支行</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_other</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>异地地区</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>江门分行</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>6</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>深圳分行</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>12</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_other</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>异地地区</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>中山分行</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>8</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>佛山分行</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_other</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>异地地区</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>肇庆分行</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>南京分行</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_other</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>异地地区</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>东莞分行</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>惠州分行</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_other</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>异地地区</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>横琴分行</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>营业</t>
+          <t>江门分行</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>region_tree</t>
+          <t>branch_other</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>异地地区</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+          <t>中山分行</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>branch_other</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>肇庆分行</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>branch_other</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>东莞分行</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>branch_other</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>横琴分行</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>branch_other</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>清远分行</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="C27" t="n">
         <v>2</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>营业</t>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>branch_other</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>汕头分行</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>branch_other</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>韶关分行</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>branch_other</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>湛江分行</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>branch_other</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>梅州分行</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>家</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1112,7 +1157,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>headcount_total</t>
+          <t>headcount</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1125,275 +1170,547 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>含劳务派遣 6589</t>
+          <t>人</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>headcount_operating</t>
+          <t>headcount</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>经营机构</t>
+          <t>劳务派遣</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4709</v>
+        <v>688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>占 79.80%</t>
+          <t>人</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>headcount_ratio</t>
+          <t>headcount</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>前中后台</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1:0.73</t>
-        </is>
+          <t>合计总数</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>6589</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>前 3254 : 中后台 2372</t>
+          <t>人</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>age_distribution</t>
+          <t>headcount</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30岁以下</t>
+          <t>总行机关</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1526</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>716</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12.13%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>age_distribution</t>
+          <t>headcount</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>31-40岁</t>
+          <t>总行直属机构</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2851</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>476</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.07%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>age_distribution</t>
+          <t>headcount</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41-50岁</t>
+          <t>经营机构</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1123</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>4709</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>79.80%</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>age_distribution</t>
+          <t>headcount</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>51岁以上</t>
+          <t>前台</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>401</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>3254</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>edu_distribution</t>
+          <t>headcount</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>硕士及以上</t>
+          <t>中后台</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1031</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>2372</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>edu_distribution</t>
+          <t>headcount</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>本科</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>4514</v>
+          <t>前中后台比</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1:0.73</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>edu_distribution</t>
+          <t>headcount</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>专科</t>
+          <t>平均年龄</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>326</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>岁</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>edu_distribution</t>
+          <t>age_dist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>专科以下</t>
+          <t>30岁以下</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>1526</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>25.86%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gender_distribution</t>
+          <t>age_dist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>31-40岁</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2717</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>2851</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>48.31%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gender_distribution</t>
+          <t>age_dist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>41-50岁</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3184</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>1123</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>19.03%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>customer_managers</t>
+          <t>age_dist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>对公客户经理</t>
+          <t>51岁以上</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>850</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>401</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>customer_managers</t>
+          <t>gender_dist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>个人客户经理</t>
+          <t>男</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>390</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>2717</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>46.04%</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>customer_managers</t>
+          <t>gender_dist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>个贷客户经理</t>
+          <t>女</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>359</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+        <v>3184</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>53.96%</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>edu_dist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>硕士研究生及以上</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1031</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>17.47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>edu_dist</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4514</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>76.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>edu_dist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>专科</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5.52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>edu_dist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>专科以下</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>30</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>customer_managers</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>客户经理合计</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1692</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>不含 172 劳务派遣</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>customer_managers</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>对公客户经理</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>850</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>customer_managers</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>个人客户经理</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>390</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>customer_managers</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>个贷客户经理</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>359</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>customer_managers</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>微贷客户经理</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C26" t="n">
         <v>93</v>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>service_managers</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>客服经理合计</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1165</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>service_managers</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>客服经理（非临柜）</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>163</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>service_managers</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>客服经理（临柜）</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1406,7 +1723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1434,12 +1751,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>social_hire_total</t>
+          <t>social_hire</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>社招入职</t>
+          <t>社招合计</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1447,183 +1764,1059 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026 年以来</t>
+          <t>人 · 2026 年以来</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>campus_hire_total</t>
+          <t>social_hire</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>校招签约</t>
+          <t>总行总经理助理级以上</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>721</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>已签约/签约中</t>
+          <t>人</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>exit_total</t>
+          <t>social_hire</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>累计退出</t>
+          <t>分支行部门班子</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>202</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1-5 月</t>
+          <t>人</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>campus_funnel</t>
+          <t>social_hire</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>全年目标</t>
+          <t>网点班子</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>659</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>campus_funnel</t>
+          <t>social_hire</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>已签约</t>
+          <t>各类客户经理</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>721</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>campus_funnel</t>
+          <t>social_hire</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>管培生</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>45</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>campus_funnel</t>
+          <t>campus_hire</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>金融科技岗</t>
+          <t>全年目标</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>54</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>659</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>campus_funnel</t>
+          <t>campus_hire</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>分行管培生</t>
+          <t>已签约/签约中</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>112</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>721</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>campus_funnel</t>
+          <t>campus_hire</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>英才岗</t>
+          <t>秋招</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>469</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>teng_long_huan_yao</t>
+          <t>campus_hire</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>腾笼换鸟</t>
+          <t>春招</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>201</v>
+        <v>430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>全年任务 410</t>
+          <t>人</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>poor_perf_exit</t>
+          <t>campus_hire</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>绩差退出</t>
+          <t>微贷/特资</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>41</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>campus_hire</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>一本及以上占比</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>+7% YoY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>campus_hire</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>总行管培生</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>campus_hire</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>总行金融科技岗</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>54</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>campus_hire</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>分行管培生</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>112</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>campus_hire</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>英才岗</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>469</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>campus_hire</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>微贷/特资定向</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>41</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>累计退出</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>202</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>人 · 2026 年以来</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>总行直属 离职</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>24</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>总行直属 退休</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>经营机构 离职</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>153</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>经营机构 退休</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>19</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>高管级退休</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>人（胡优华资深督导）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>中层干部 离职</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>员工 离职</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>175</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>员工 退休</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>24</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>teng_long</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>全年任务</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>410</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>teng_long</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1-5月累计退出</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>201</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>teng_long</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>任务完成率</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>teng_long</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>完成率 Top1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>总营 295%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>序时</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>teng_long</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>完成率 Top2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>惠州 259%</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>序时</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>teng_long</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>完成率 Top3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>东莞 255%</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>序时</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>teng_long</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>完成量 Top1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>广分 28人</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>teng_long</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>完成量 Top2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>深圳 23人</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>teng_long</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>完成量 Top3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>海珠 20人</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>teng_long</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>完成率 Bottom1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>佛山 44%</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>序时</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>teng_long</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>完成率 Bottom2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>汕头 48%</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>序时</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>teng_long</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>完成率 Bottom3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>广分 80%</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>序时</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>poor_perf</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>目标退出率</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>绩差客户经理</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>poor_perf</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1-5月累计退出</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
         <v>44</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>目标 50%（96人）</t>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>poor_perf</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>完成率</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>占绩差总人数</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>poor_perf</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>退出率 Top1-5</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>开发区/南沙/江门/汕头/梅州 100%</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>并列</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>poor_perf</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>退出人数 Top1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>深圳 8人</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>poor_perf</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>退出人数 Top2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>东莞 7人</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>poor_perf</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>退出人数 Top3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>海珠 6人</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>poor_perf</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>退出率 Bottom1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>南京 20%</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>poor_perf</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>退出率 Bottom2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>中山 20%</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>poor_perf</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>退出率 Bottom3</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>深圳 27%</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1-5月发生</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>15</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>已结案</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>11</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>胜诉</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>人（广州分行、信用卡中心）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>败诉</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>人（汕头分行、信用卡中心）</t>
         </is>
       </c>
     </row>
@@ -1638,7 +2831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,265 +2859,442 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>headcount_total</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>中层总职数</t>
+          <t>中层干部总职数</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>211</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>headcount_filled</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>已配备</t>
+          <t>总行部门</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>人</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>headcount_vacancy</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>空缺</t>
+          <t>经营机构</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>人</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>config_table</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>市管领导干部</t>
+          <t>中层正职</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
+        <v>54</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>config_table</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>高管人员</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>/</t>
+          <t>中层副职</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>157</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>人</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>config_table</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>派驻纪检监察组</t>
+          <t>已配备</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
+        <v>194</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>人（92%）</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>config_table</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中层正职</t>
+          <t>尚空缺</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>54</v>
-      </c>
-      <c r="D8" t="n">
-        <v>50</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
+        <v>17</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>人（8%）</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>config_table</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中层副职</t>
+          <t>总行已配备</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>157</v>
-      </c>
-      <c r="D9" t="n">
-        <v>144</v>
-      </c>
-      <c r="E9" t="n">
-        <v>13</v>
+        <v>93</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>人（空缺 7）</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>config_table</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>总行部门</t>
+          <t>经营已配备</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D10" t="n">
-        <v>93</v>
-      </c>
-      <c r="E10" t="n">
-        <v>7</v>
+        <v>101</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>人（空缺 10）</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>config_table</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>经营机构</t>
+          <t>正职已配备</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
-      </c>
-      <c r="D11" t="n">
-        <v>101</v>
-      </c>
-      <c r="E11" t="n">
-        <v>10</v>
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>人（空缺 4）</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>adjustments</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>提拔</t>
+          <t>副职已配备</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>人次</t>
+          <t>人（空缺 13）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>adjustments</t>
+          <t>position_table</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>降免职</t>
+          <t>市管领导干部</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>人次</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>position_table</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>高管人员</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>含工会主席、行长助理、首席风险官、首席信息官</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>position_table</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>派驻纪检监察组（不含组长）</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>position_table</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>中层正职</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>54</v>
+      </c>
+      <c r="D16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>副总级一把手 17 名</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>position_table</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>中层副职</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>157</v>
+      </c>
+      <c r="D17" t="n">
+        <v>144</v>
+      </c>
+      <c r="E17" t="n">
+        <v>13</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>副总 67 + 总助 74 + 经理 3，含 3 纪检</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>position_table</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>总行部门班子</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>100</v>
+      </c>
+      <c r="D18" t="n">
+        <v>93</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>position_table</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>经营机构班子</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>111</v>
+      </c>
+      <c r="D19" t="n">
+        <v>101</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>含 3 纪检</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>adjustments</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>提拔</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>94</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>人次</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adjustments</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>降职、免职（含受处分）</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>14</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>人次</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adjustments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>到龄转岗</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C22" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>人次</t>
         </is>
@@ -1941,7 +3311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1969,7 +3339,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>salary_total</t>
+          <t>salary</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1979,152 +3349,302 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15 亿元</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>salary_per_capita</t>
+          <t>salary</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>人均薪酬</t>
+          <t>2025 年人均薪酬</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>24.3 万元</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>含预发 2026 开门红 0.3 亿</t>
+          <t>万元（含预发 2026 开门红 0.3 亿）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pension_balance</t>
+          <t>salary</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>企业年金余额</t>
+          <t>2026 年 1-5 月已发放</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17.44 亿元</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026.5</t>
+          <t>亿元</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tou_lang_count</t>
+          <t>pension</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>头狼评选</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>129</v>
+          <t>2025 年企业年金余额</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16.37</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026 Q1</t>
+          <t>亿元</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>monitoring</t>
+          <t>pension</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>监测人数</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>95</v>
+          <t>2026.5 余额</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>17.44</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>班子成员</t>
+          <t>亿元</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>monitoring</t>
+          <t>pension</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>监测人次</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>113</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>业绩监测</t>
-        </is>
-      </c>
+          <t>个人缴费比例</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>monitoring</t>
+          <t>pension</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>黑榜人数</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>15</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>督导函</t>
-        </is>
-      </c>
+          <t>单位缴费比例</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>pension</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025 补充医疗缴费</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7979</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>pension</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>节余总额</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>亿元（含个人 + 单位住院）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pension</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026.5 节余</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>亿元（个人 1.6 + 单位 3002 万）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>监测人数</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>95</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>经营机构班子成员（不含到龄转岗及离职脱密期）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>监测人次</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>113</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>人 · 2026 Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>黑榜人数</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>人（首次触发监测督导）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>黑榜人次</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C15" t="n">
         <v>16</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>首次触发</t>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>人次 · 书面督导函</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>头狼评选</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>129</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>人 · 2026 Q1</t>
         </is>
       </c>
     </row>
@@ -2139,7 +3659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2167,7 +3687,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>training_total</t>
+          <t>training</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2178,12 +3698,16 @@
       <c r="C2" t="n">
         <v>983</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>场</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>key_projects</t>
+          <t>training</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2194,223 +3718,435 @@
       <c r="C3" t="n">
         <v>55</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>exam_count</t>
+          <t>training</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>上岗资格人次</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1878</v>
+          <t>重点项目执行率</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>58.06%</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>35 场次</t>
+          <t>近期启动『走进华为 2.0』</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>key_projects_pct</t>
+          <t>key_projects</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>重点项目执行率</t>
+          <t>广银大讲堂</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5806</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>已完成 32/55</t>
+          <t>期</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dept_execution</t>
+          <t>key_projects</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>董事会办公室</t>
+          <t>对公特训营</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>期</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dept_execution</t>
+          <t>key_projects</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>私人银行部</t>
+          <t>个贷铁军培训</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>期</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dept_execution</t>
+          <t>key_projects</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>金融同业部</t>
+          <t>办贷能力提升火线班</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>期</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dept_execution</t>
+          <t>key_projects</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金融市场部</t>
+          <t>校招新员工集中培训</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>期</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dept_execution</t>
+          <t>dept_top</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>战略客户部</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>董事会办公室</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dept_execution</t>
+          <t>dept_top</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>消保部</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>100</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>私人银行与财富管理部</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dept_execution</t>
+          <t>dept_top</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>机关纪委</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>100</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>金融同业部</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dept_execution</t>
+          <t>dept_top</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>安全保卫部</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>金融市场部</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dept_execution</t>
+          <t>dept_top</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>金融科技部</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>战略客户部</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dept_execution</t>
+          <t>dept_top</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>内控合规部</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>消费者权益保护部</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dept_execution</t>
+          <t>dept_top</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>机关纪委办公室</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dept_top</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>安全保卫部</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dept_bottom</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>金融科技部</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>完成率</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>dept_bottom</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>内控合规部</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>完成率</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>dept_bottom</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>运营管理部</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>14.29%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>完成率</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>exam</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>上岗资格考试</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>35</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>场次</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>exam</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>参考人次</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1878</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>人次</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exam</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>涉及岗位</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>大岗位</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/test.xlsx
+++ b/data/test.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="组织架构" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工情况" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员优化" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="干部队伍" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考核薪酬" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="培训赋能" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M-1 组织架构" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M-2 员工情况" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M-3 人员优化" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M-4 干部队伍" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M-4 干部职数表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M-5 考核薪酬" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M-6 培训赋能" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +479,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#1e5baa</t>
+          <t>#4f46e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>副色</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>#f97316</t>
         </is>
       </c>
     </row>
@@ -493,35 +506,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>section</t>
+          <t>分组</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sub</t>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_total</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>headquarters</t>
+          <t>总行架构</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,19 +557,32 @@
           <t>总行本部一级部门</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>28</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>个</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>headquarters</t>
+          <t>总行架构</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -549,19 +590,28 @@
           <t>总行直属一级部门</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>2</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>个</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>headquarters</t>
+          <t>总行架构</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -569,19 +619,28 @@
           <t>总行直属二级部门</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>13</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>个</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>branches</t>
+          <t>全行机构</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -589,19 +648,36 @@
           <t>分行级机构</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>24</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>家（含总行营业部、信用卡中心）</t>
+          <t>家</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>含总行营业部、信用卡中心</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>branches</t>
+          <t>全行机构</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -609,19 +685,36 @@
           <t>全行网点</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>183</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>家</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>营业 179 + 停业 4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>branches</t>
+          <t>营业状态</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -629,19 +722,28 @@
           <t>正常营业</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>179</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>branches</t>
+          <t>营业状态</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +751,28 @@
           <t>临时停业</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>4</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>branch_guangzhou</t>
+          <t>广州地区</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,19 +780,28 @@
           <t>行总营业部</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>branch_guangzhou</t>
+          <t>广州地区</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -689,19 +809,28 @@
           <t>广州分行</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>37</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>branch_guangzhou</t>
+          <t>广州地区</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -709,19 +838,28 @@
           <t>海珠中心支行</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>22</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>branch_guangzhou</t>
+          <t>广州地区</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -729,19 +867,28 @@
           <t>天河中心支行</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>14</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>branch_guangzhou</t>
+          <t>广州地区</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -749,19 +896,28 @@
           <t>白云中心支行</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>12</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>branch_guangzhou</t>
+          <t>广州地区</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -769,19 +925,28 @@
           <t>开发区中心支行</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>11</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>branch_guangzhou</t>
+          <t>广州地区</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -789,19 +954,28 @@
           <t>增城中心支行</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>4</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>branch_guangzhou</t>
+          <t>广州地区</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -809,19 +983,28 @@
           <t>南沙分行</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>5</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>branch_guangzhou</t>
+          <t>广州地区</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -829,19 +1012,28 @@
           <t>科技支行</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>1</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>branch_other</t>
+          <t>异地地区</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -849,19 +1041,28 @@
           <t>深圳分行</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>12</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>branch_other</t>
+          <t>异地地区</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -869,19 +1070,28 @@
           <t>佛山分行</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>12</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>branch_other</t>
+          <t>异地地区</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -889,19 +1099,28 @@
           <t>南京分行</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>9</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>branch_other</t>
+          <t>异地地区</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -909,19 +1128,28 @@
           <t>惠州分行</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>7</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>branch_other</t>
+          <t>异地地区</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -929,19 +1157,28 @@
           <t>江门分行</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>6</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>branch_other</t>
+          <t>异地地区</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -949,19 +1186,28 @@
           <t>中山分行</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>8</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>branch_other</t>
+          <t>异地地区</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -969,19 +1215,28 @@
           <t>肇庆分行</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>4</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>branch_other</t>
+          <t>异地地区</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -989,19 +1244,28 @@
           <t>东莞分行</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>8</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>branch_other</t>
+          <t>异地地区</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1009,19 +1273,28 @@
           <t>横琴分行</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>4</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>branch_other</t>
+          <t>异地地区</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1029,19 +1302,28 @@
           <t>清远分行</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>2</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>branch_other</t>
+          <t>异地地区</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1049,19 +1331,28 @@
           <t>汕头分行</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>1</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>branch_other</t>
+          <t>异地地区</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1069,19 +1360,28 @@
           <t>韶关分行</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>1</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>branch_other</t>
+          <t>异地地区</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1089,19 +1389,28 @@
           <t>湛江分行</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>branch_other</t>
+          <t>异地地区</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1109,14 +1418,23 @@
           <t>梅州分行</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>1</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>家</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1129,95 +1447,153 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>section</t>
+          <t>分组</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sub</t>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_total</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>headcount</t>
+          <t>合计总数</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>正式员工</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>5901</v>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6589</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>人</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>含劳务派遣</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>headcount</t>
+          <t>合计总数</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>劳务派遣</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>688</v>
+          <t>正式员工</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>人</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>不含劳务派遣</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>headcount</t>
+          <t>合计总数</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>合计总数</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>6589</v>
+          <t>劳务派遣</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>headcount</t>
+          <t>员工构成</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1225,19 +1601,32 @@
           <t>总行机关</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>716</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>12.13%</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>headcount</t>
+          <t>员工构成</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1245,19 +1634,32 @@
           <t>总行直属机构</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>476</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>8.07%</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>headcount</t>
+          <t>员工构成</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1265,64 +1667,103 @@
           <t>经营机构</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>4709</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4709</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>79.80%</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>headcount</t>
+          <t>前后台</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>前台</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3254</v>
+          <t>前台部门</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3254</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>人</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>不含信用卡中心</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>headcount</t>
+          <t>前后台</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中后台</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2372</v>
+          <t>中后台部门</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2372</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>headcount</t>
+          <t>前后台</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>前中后台比</t>
+          <t>前后台比例</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1331,386 +1772,591 @@
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>前台:中后台</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>headcount</t>
+          <t>年龄分布</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>平均年龄</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>36</v>
+          <t>30岁以下</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>岁</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>25.86%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>age_dist</t>
+          <t>年龄分布</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30岁以下</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1526</v>
+          <t>31-40岁</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2851</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25.86%</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>48.31%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>age_dist</t>
+          <t>年龄分布</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>31-40岁</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2851</v>
+          <t>41-50岁</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.31%</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>19.03%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>age_dist</t>
+          <t>年龄分布</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>41-50岁</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1123</v>
+          <t>51岁以上</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19.03%</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>age_dist</t>
+          <t>学历分布</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>51岁以上</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>401</v>
+          <t>硕士研究生及以上</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6.80%</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>17.47%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gender_dist</t>
+          <t>学历分布</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>男</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2717</v>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4514</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.04%</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>76.50%</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gender_dist</t>
+          <t>学历分布</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>女</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>3184</v>
+          <t>专科</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.96%</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>5.52%</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>edu_dist</t>
+          <t>学历分布</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>硕士研究生及以上</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1031</v>
+          <t>专科以下</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>17.47%</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>edu_dist</t>
+          <t>性别比例</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>本科</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>4514</v>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2717</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>76.50%</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>46.04%</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>edu_dist</t>
+          <t>性别比例</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>专科</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>326</v>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3184</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5.52%</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>53.96%</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>edu_dist</t>
+          <t>客户经理</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>专科以下</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>30</v>
+          <t>客户经理合计</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1692</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>不含 172 劳务派遣</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>customer_managers</t>
+          <t>客户经理</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>客户经理合计</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1692</v>
+          <t>对公客户经理</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>不含 172 劳务派遣</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>customer_managers</t>
+          <t>客户经理</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>对公客户经理</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>850</v>
+          <t>个人客户经理</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>customer_managers</t>
+          <t>客户经理</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>个人客户经理</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>390</v>
+          <t>个贷客户经理</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>customer_managers</t>
+          <t>客户经理</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>个贷客户经理</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>359</v>
+          <t>微贷客户经理</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>customer_managers</t>
+          <t>客服经理</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>微贷客户经理</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>93</v>
+          <t>客服经理合计</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1165</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>人</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>service_managers</t>
+          <t>客服经理</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>客服经理合计</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1165</v>
+          <t>客服经理（非临柜）</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>service_managers</t>
+          <t>客服经理</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>客服经理（非临柜）</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>163</v>
+          <t>客服经理（临柜）</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>service_managers</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>客服经理（临柜）</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1002</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>人</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1723,35 +2369,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>section</t>
+          <t>分组</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sub</t>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_total</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>social_hire</t>
+          <t>社招</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1759,19 +2420,36 @@
           <t>社招合计</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>34</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>人 · 2026 年以来</t>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026 年以来</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>social_hire</t>
+          <t>社招</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1779,19 +2457,28 @@
           <t>总行总经理助理级以上</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>2</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>social_hire</t>
+          <t>社招</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1799,19 +2486,28 @@
           <t>分支行部门班子</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>4</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>social_hire</t>
+          <t>社招</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1819,19 +2515,28 @@
           <t>网点班子</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>4</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>social_hire</t>
+          <t>社招</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1839,19 +2544,28 @@
           <t>各类客户经理</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>9</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>social_hire</t>
+          <t>社招</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1859,19 +2573,28 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>15</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>campus_hire</t>
+          <t>校招阶段</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1879,19 +2602,28 @@
           <t>全年目标</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>659</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>campus_hire</t>
+          <t>校招阶段</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1899,19 +2631,32 @@
           <t>已签约/签约中</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>721</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>人</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>campus_hire</t>
+          <t>校招阶段</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1919,19 +2664,28 @@
           <t>秋招</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>250</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>campus_hire</t>
+          <t>校招阶段</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1939,19 +2693,28 @@
           <t>春招</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>430</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>campus_hire</t>
+          <t>校招阶段</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1959,19 +2722,28 @@
           <t>微贷/特资</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>41</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>campus_hire</t>
+          <t>校招阶段</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1981,19 +2753,30 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>+7% YoY</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>较去年提升 7%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>campus_hire</t>
+          <t>校招岗位</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2001,19 +2784,28 @@
           <t>总行管培生</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>45</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>campus_hire</t>
+          <t>校招岗位</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,19 +2813,28 @@
           <t>总行金融科技岗</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>54</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>campus_hire</t>
+          <t>校招岗位</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2041,19 +2842,28 @@
           <t>分行管培生</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>112</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>campus_hire</t>
+          <t>校招岗位</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2061,19 +2871,28 @@
           <t>英才岗</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>469</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>campus_hire</t>
+          <t>校招岗位</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2081,19 +2900,28 @@
           <t>微贷/特资定向</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>41</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>退出</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2101,19 +2929,36 @@
           <t>累计退出</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>202</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>人 · 2026 年以来</t>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026 年以来</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>退出</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2121,19 +2966,28 @@
           <t>总行直属 离职</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>24</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>退出</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2141,19 +2995,28 @@
           <t>总行直属 退休</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>6</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>退出</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2161,19 +3024,28 @@
           <t>经营机构 离职</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>153</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>退出</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2181,39 +3053,61 @@
           <t>经营机构 退休</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>19</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>退出职级</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>高管级退休</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
+          <t>高管级 退休</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>人（胡优华资深督导）</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>胡优华资深督导</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>退出职级</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2221,19 +3115,28 @@
           <t>中层干部 离职</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>2</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>退出职级</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2241,19 +3144,28 @@
           <t>员工 离职</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>175</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>退出职级</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2261,19 +3173,28 @@
           <t>员工 退休</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>24</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>teng_long</t>
+          <t>腾笼换鸟</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2281,39 +3202,57 @@
           <t>全年任务</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>410</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>teng_long</t>
+          <t>腾笼换鸟</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1-5月累计退出</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>201</v>
+          <t>1-5月完成</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>teng_long</t>
+          <t>腾笼换鸟</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2323,15 +3262,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>teng_long</t>
+          <t>腾笼换鸟</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2341,19 +3295,30 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>总营 295%</t>
+          <t>295</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>序时</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>总营</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>teng_long</t>
+          <t>腾笼换鸟</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2363,19 +3328,30 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>惠州 259%</t>
+          <t>259</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>序时</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>惠州</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>teng_long</t>
+          <t>腾笼换鸟</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2385,19 +3361,30 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>东莞 255%</t>
+          <t>255</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>序时</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>东莞</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>teng_long</t>
+          <t>腾笼换鸟</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2407,7 +3394,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>广分 28人</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2415,11 +3402,22 @@
           <t>人</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>广分</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>teng_long</t>
+          <t>腾笼换鸟</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2429,7 +3427,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>深圳 23人</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2437,11 +3435,22 @@
           <t>人</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>teng_long</t>
+          <t>腾笼换鸟</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2451,7 +3460,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>海珠 20人</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2459,11 +3468,22 @@
           <t>人</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>海珠</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>teng_long</t>
+          <t>腾笼换鸟</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2473,19 +3493,30 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>佛山 44%</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>序时</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>teng_long</t>
+          <t>腾笼换鸟</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2495,19 +3526,30 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>汕头 48%</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>序时</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>汕头</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>teng_long</t>
+          <t>腾笼换鸟</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2517,19 +3559,30 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>广分 80%</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>序时</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>广分</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>poor_perf</t>
+          <t>绩差退出</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2539,39 +3592,59 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>绩差客户经理</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>poor_perf</t>
+          <t>绩差退出</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1-5月累计退出</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>44</v>
+          <t>累计退出</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>poor_perf</t>
+          <t>绩差退出</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2581,19 +3654,34 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>占绩差总人数</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>poor_perf</t>
+          <t>绩差退出</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2603,19 +3691,30 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>开发区/南沙/江门/汕头/梅州 100%</t>
+          <t>100</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>并列</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>开发区/南沙/江门/汕头/梅州</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>poor_perf</t>
+          <t>绩差退出</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2625,15 +3724,30 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>深圳 8人</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>poor_perf</t>
+          <t>绩差退出</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2643,15 +3757,30 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>东莞 7人</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>东莞</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>poor_perf</t>
+          <t>绩差退出</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2661,15 +3790,30 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>海珠 6人</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>海珠</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>poor_perf</t>
+          <t>绩差退出</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2679,15 +3823,30 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>南京 20%</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>poor_perf</t>
+          <t>绩差退出</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2697,15 +3856,30 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>中山 20%</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>中山</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>poor_perf</t>
+          <t>绩差退出</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2715,35 +3889,63 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>深圳 27%</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>劳动仲裁</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1-5月发生</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>15</v>
+          <t>1-5月总数</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>人</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>劳动仲裁</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2751,19 +3953,32 @@
           <t>已结案</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>4</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>胜诉 2 + 败诉 2</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>劳动仲裁</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2771,19 +3986,28 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>11</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>劳动仲裁</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2791,19 +4015,32 @@
           <t>胜诉</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>2</v>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>人（广州分行、信用卡中心）</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>广分、信用卡</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>劳动仲裁</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2811,14 +4048,27 @@
           <t>败诉</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>2</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>人（汕头分行、信用卡中心）</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>汕头、信用卡</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2831,35 +4081,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>section</t>
+          <t>分组</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sub</t>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_total</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>中层总览</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2867,19 +4132,32 @@
           <t>中层干部总职数</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>211</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>人</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>中层总览</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2887,19 +4165,28 @@
           <t>总行部门</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>100</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>中层总览</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2907,19 +4194,28 @@
           <t>经营机构</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>111</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>中层总览</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2927,19 +4223,28 @@
           <t>中层正职</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>54</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>中层总览</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2947,19 +4252,28 @@
           <t>中层副职</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>157</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>配备情况</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2967,19 +4281,36 @@
           <t>已配备</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>194</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>人（92%）</t>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>配备情况</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2987,318 +4318,378 @@
           <t>尚空缺</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>17</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>人（8%）</t>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>配备-总行</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>总行已配备</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>93</v>
+          <t>已配备</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>人（空缺 7）</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>空缺 7</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>配备-总行</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>经营已配备</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>101</v>
+          <t>空缺</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>人（空缺 10）</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>配备-经营</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>正职已配备</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
+          <t>已配备</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>人（空缺 4）</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>空缺 10</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>配备-经营</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>副职已配备</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>144</v>
+          <t>空缺</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>人（空缺 13）</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>position_table</t>
+          <t>配备-正职</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>市管领导干部</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" t="n">
-        <v>8</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>已配备</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>副总级一把手 17 名</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>position_table</t>
+          <t>配备-正职</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>高管人员</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>6</v>
-      </c>
+          <t>空缺</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>含工会主席、行长助理、首席风险官、首席信息官</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>position_table</t>
+          <t>配备-副职</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>派驻纪检监察组（不含组长）</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>已配备</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>副总 67+总助 74+经理 3</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>position_table</t>
+          <t>配备-副职</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中层正职</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>54</v>
-      </c>
-      <c r="D16" t="n">
-        <v>50</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4</v>
+          <t>空缺</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>含 3 纪检</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>副总级一把手 17 名</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>position_table</t>
+          <t>调整情况</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中层副职</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>157</v>
-      </c>
-      <c r="D17" t="n">
-        <v>144</v>
-      </c>
-      <c r="E17" t="n">
-        <v>13</v>
-      </c>
+          <t>提拔</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>人次</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>副总 67 + 总助 74 + 经理 3，含 3 纪检</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>position_table</t>
+          <t>调整情况</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>总行部门班子</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>100</v>
-      </c>
-      <c r="D18" t="n">
-        <v>93</v>
-      </c>
-      <c r="E18" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>降职、免职</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>人次</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>含受处分</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>position_table</t>
+          <t>调整情况</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>经营机构班子</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>111</v>
-      </c>
-      <c r="D19" t="n">
-        <v>101</v>
-      </c>
-      <c r="E19" t="n">
-        <v>10</v>
-      </c>
+          <t>到龄转岗</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>人次</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>含 3 纪检</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adjustments</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>提拔</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>94</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>人次</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adjustments</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>降职、免职（含受处分）</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>14</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>人次</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adjustments</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>到龄转岗</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>13</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>人次</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3311,340 +4702,214 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>section</t>
+          <t>分类</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>总职数</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>已配备</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sub</t>
+          <t>空缺</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>salary</t>
+          <t>市管领导干部</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025 年工资总额</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>亿元</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>salary</t>
+          <t>高管人员</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025 年人均薪酬</t>
+          <t>/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>万元（含预发 2026 开门红 0.3 亿）</t>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>含工会主席、行长助理、首席风险官、首席信息官</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>salary</t>
+          <t>派驻纪检监察组</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026 年 1-5 月已发放</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>不含组长</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pension</t>
+          <t>中层正职</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025 年企业年金余额</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16.37</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>副总级一把手 17 名</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pension</t>
+          <t>中层副职</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026.5 余额</t>
+          <t>157</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>144</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>副总 67 + 总助 74 + 经理 3，含 3 纪检</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pension</t>
+          <t>总行部门班子</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>个人缴费比例</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pension</t>
+          <t>经营机构班子</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>单位缴费比例</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>pension</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2025 补充医疗缴费</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7979</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>万元</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>pension</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>节余总额</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>亿元（含个人 + 单位住院）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>pension</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026.5 节余</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>亿元（个人 1.6 + 单位 3002 万）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>monitoring</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>监测人数</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>95</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>经营机构班子成员（不含到龄转岗及离职脱密期）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>monitoring</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>监测人次</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>113</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>人 · 2026 Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>monitoring</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>黑榜人数</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>15</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>人（首次触发监测督导）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>monitoring</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>黑榜人次</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>16</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>人次 · 书面督导函</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>monitoring</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>头狼评选</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>129</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>人 · 2026 Q1</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>含 3 纪检</t>
         </is>
       </c>
     </row>
@@ -3659,479 +4924,1311 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>section</t>
+          <t>分组</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sub</t>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_total</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>薪酬</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>能力大提升项目</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>983</v>
+          <t>2025 年工资总额</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>场</t>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>薪酬</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>重点培训项目</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>55</v>
+          <t>2025 年人均薪酬</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>24.3</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>个</t>
-        </is>
-      </c>
+          <t>万元</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>含预发 2026 开门红 0.3 亿元</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>薪酬</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>重点项目执行率</t>
+          <t>2026 年 1-5 月已发放</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>58.06%</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>近期启动『走进华为 2.0』</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>key_projects</t>
+          <t>年金</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>广银大讲堂</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>5</v>
+          <t>2025 年企业年金余额</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16.37</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>期</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>key_projects</t>
+          <t>年金</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>对公特训营</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
+          <t>2026.5 余额</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>17.44</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>期</t>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>key_projects</t>
+          <t>年金</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>个贷铁军培训</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
+          <t>个人缴费比例</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>期</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>key_projects</t>
+          <t>年金</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>办贷能力提升火线班</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>4</v>
+          <t>单位缴费比例</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>期</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>key_projects</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>校招新员工集中培训</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
+          <t>2025 补充医疗缴费</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7979</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>期</t>
-        </is>
-      </c>
+          <t>万元</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dept_top</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>董事会办公室</t>
+          <t>2025 节余总额</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>完成</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>含个人 + 单位住院</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dept_top</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>私人银行与财富管理部</t>
+          <t>2026.5 节余</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>个人 1.6 + 单位 3002 万</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dept_top</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>金融同业部</t>
+          <t>个人节余</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>完成</t>
-        </is>
-      </c>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dept_top</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>金融市场部</t>
+          <t>单位节余</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>完成</t>
-        </is>
-      </c>
+          <t>万元</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dept_top</t>
+          <t>监测</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>战略客户部</t>
+          <t>监测人数</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>完成</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>经营机构班子成员（不含到龄转岗及离职脱密期）</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dept_top</t>
+          <t>监测</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>消费者权益保护部</t>
+          <t>监测人次</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>113</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>完成</t>
-        </is>
-      </c>
+          <t>人次</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026 Q1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dept_top</t>
+          <t>监测</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>机关纪委办公室</t>
+          <t>黑榜人数</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>完成</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>首次触发监测督导</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dept_top</t>
+          <t>监测</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>安全保卫部</t>
+          <t>黑榜人次</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>完成</t>
-        </is>
-      </c>
+          <t>人次</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>书面督导函</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dept_bottom</t>
+          <t>头狼</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>金融科技部</t>
+          <t>头狼评选</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>129</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>完成率</t>
-        </is>
-      </c>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026 Q1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>培训总量</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>能力大提升项目</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>场</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>培训总量</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>重点培训项目</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>重点项目</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>广银大讲堂</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>期</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>重点项目</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>对公特训营</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>期</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>重点项目</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>个贷铁军培训</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>期</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>重点项目</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>办贷能力提升火线班</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>期</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>重点项目</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>校招新员工集中培训</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>期</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>重点项目</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>走进华为 2.0 领导力</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>期</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>近期启动</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>执行率</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>重点项目已执行</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>58.06</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>近期启动『走进华为 2.0』</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>100% 部门</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>董事会办公室</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>100% 部门</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>私人银行与财富管理部</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>100% 部门</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金融同业部</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>100% 部门</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>金融市场部</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>100% 部门</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>战略客户部</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>100% 部门</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>消费者权益保护部</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>100% 部门</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>机关纪委办公室</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>100% 部门</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>安全保卫部</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dept_bottom</t>
+          <t>末位部门</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>内控合规部</t>
+          <t>金融科技部</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>完成率</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>dept_bottom</t>
+          <t>末位部门</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>运营管理部</t>
+          <t>内控合规部</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14.29%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>完成率</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>exam</t>
+          <t>末位部门</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>上岗资格考试</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>35</v>
+          <t>运营管理部</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>14.29</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>场次</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>完成率</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>exam</t>
+          <t>资格考</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>参考人次</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1878</v>
+          <t>上岗资格考试</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>人次</t>
-        </is>
-      </c>
+          <t>场次</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>exam</t>
+          <t>资格考</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4139,12 +6236,54 @@
           <t>涉及岗位</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>8</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>大岗位</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>资格考</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>参考人次</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>人次</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
